--- a/results.xlsx
+++ b/results.xlsx
@@ -160,371 +160,460 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Results!$A$2:$A$59</c:f>
+              <c:f>Results!$A$3:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
-                  <c:v>10067</c:v>
+                  <c:v>0.049</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10115</c:v>
+                  <c:v>0.381</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11649</c:v>
+                  <c:v>0.6820000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13150</c:v>
+                  <c:v>0.984</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14652</c:v>
+                  <c:v>1.286</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16156</c:v>
+                  <c:v>1.59</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>17660</c:v>
+                  <c:v>1.891</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19162</c:v>
+                  <c:v>2.193</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20664</c:v>
+                  <c:v>2.495</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>22168</c:v>
+                  <c:v>2.798</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>23672</c:v>
+                  <c:v>3.102</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25174</c:v>
+                  <c:v>3.404</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>26676</c:v>
+                  <c:v>3.706</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>28180</c:v>
+                  <c:v>4.007</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>29683</c:v>
+                  <c:v>4.309</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>31185</c:v>
+                  <c:v>4.613</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>32688</c:v>
+                  <c:v>4.915</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>34192</c:v>
+                  <c:v>5.217000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>35695</c:v>
+                  <c:v>5.519</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>37197</c:v>
+                  <c:v>5.82</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38700</c:v>
+                  <c:v>6.125</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>40204</c:v>
+                  <c:v>6.427</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>41707</c:v>
+                  <c:v>6.729</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>43209</c:v>
+                  <c:v>7.031000000000001</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>44711</c:v>
+                  <c:v>7.333</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46216</c:v>
+                  <c:v>7.636</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>47719</c:v>
+                  <c:v>7.938</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>49221</c:v>
+                  <c:v>8.24</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>50723</c:v>
+                  <c:v>8.542</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>52228</c:v>
+                  <c:v>8.843999999999999</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>53731</c:v>
+                  <c:v>9.147</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>55233</c:v>
+                  <c:v>9.449</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>56735</c:v>
+                  <c:v>9.752000000000001</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>58240</c:v>
+                  <c:v>10.054</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>59743</c:v>
+                  <c:v>10.356</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>61245</c:v>
+                  <c:v>10.66</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>62747</c:v>
+                  <c:v>10.961</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>64251</c:v>
+                  <c:v>11.263</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>65755</c:v>
+                  <c:v>11.565</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>67257</c:v>
+                  <c:v>11.867</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>68759</c:v>
+                  <c:v>12.171</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>70263</c:v>
+                  <c:v>12.472</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>71767</c:v>
+                  <c:v>12.774</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>73269</c:v>
+                  <c:v>13.076</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>74771</c:v>
+                  <c:v>13.379</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>76275</c:v>
+                  <c:v>13.683</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>77778</c:v>
+                  <c:v>13.985</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>79281</c:v>
+                  <c:v>14.287</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>80783</c:v>
+                  <c:v>14.588</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>82286</c:v>
+                  <c:v>14.89</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>83790</c:v>
+                  <c:v>15.194</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>85293</c:v>
+                  <c:v>15.496</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>86795</c:v>
+                  <c:v>15.798</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>88298</c:v>
+                  <c:v>16.099</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>89802</c:v>
+                  <c:v>16.401</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>91304</c:v>
+                  <c:v>16.706</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>92807</c:v>
+                  <c:v>17.008</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>94310</c:v>
+                  <c:v>17.31</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17.612</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17.914</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18.218</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>18.519</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>18.821</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>19.123</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>19.425</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19.728</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>20.03</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>20.333</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>20.635</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>20.937</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>21.241</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>21.543</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Results!$B$2:$B$59</c:f>
+              <c:f>Results!$B$3:$B$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>27</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>27</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>28</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>28</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>27</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>27</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>13</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>13</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>28</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>28</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>13</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>13</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>28</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>28</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>12</c:v>
+                  <c:v>254</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>28</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>28</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>13</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>13</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>28</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>28</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>28</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>28</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>12</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>29</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>29</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>13</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>13</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>28</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>28</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>28</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>28</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>28</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>28</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>12</c:v>
+                  <c:v>251</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>12</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>28</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>28</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>12</c:v>
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
         </c:ser>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:scatterChart>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -534,7 +623,7 @@
           <c:spPr>
             <a:ln w="25400">
               <a:solidFill>
-                <a:srgbClr val="FFFF00"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
             </a:ln>
@@ -544,373 +633,457 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Results!$A$2:$A$59</c:f>
+              <c:f>Results!$A$3:$A$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
-                  <c:v>10067</c:v>
+                  <c:v>0.049</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10115</c:v>
+                  <c:v>0.381</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11649</c:v>
+                  <c:v>0.6820000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13150</c:v>
+                  <c:v>0.984</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14652</c:v>
+                  <c:v>1.286</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16156</c:v>
+                  <c:v>1.59</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>17660</c:v>
+                  <c:v>1.891</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19162</c:v>
+                  <c:v>2.193</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20664</c:v>
+                  <c:v>2.495</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>22168</c:v>
+                  <c:v>2.798</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>23672</c:v>
+                  <c:v>3.102</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25174</c:v>
+                  <c:v>3.404</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>26676</c:v>
+                  <c:v>3.706</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>28180</c:v>
+                  <c:v>4.007</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>29683</c:v>
+                  <c:v>4.309</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>31185</c:v>
+                  <c:v>4.613</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>32688</c:v>
+                  <c:v>4.915</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>34192</c:v>
+                  <c:v>5.217000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>35695</c:v>
+                  <c:v>5.519</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>37197</c:v>
+                  <c:v>5.82</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38700</c:v>
+                  <c:v>6.125</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>40204</c:v>
+                  <c:v>6.427</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>41707</c:v>
+                  <c:v>6.729</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>43209</c:v>
+                  <c:v>7.031000000000001</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>44711</c:v>
+                  <c:v>7.333</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46216</c:v>
+                  <c:v>7.636</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>47719</c:v>
+                  <c:v>7.938</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>49221</c:v>
+                  <c:v>8.24</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>50723</c:v>
+                  <c:v>8.542</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>52228</c:v>
+                  <c:v>8.843999999999999</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>53731</c:v>
+                  <c:v>9.147</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>55233</c:v>
+                  <c:v>9.449</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>56735</c:v>
+                  <c:v>9.752000000000001</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>58240</c:v>
+                  <c:v>10.054</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>59743</c:v>
+                  <c:v>10.356</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>61245</c:v>
+                  <c:v>10.66</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>62747</c:v>
+                  <c:v>10.961</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>64251</c:v>
+                  <c:v>11.263</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>65755</c:v>
+                  <c:v>11.565</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>67257</c:v>
+                  <c:v>11.867</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>68759</c:v>
+                  <c:v>12.171</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>70263</c:v>
+                  <c:v>12.472</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>71767</c:v>
+                  <c:v>12.774</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>73269</c:v>
+                  <c:v>13.076</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>74771</c:v>
+                  <c:v>13.379</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>76275</c:v>
+                  <c:v>13.683</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>77778</c:v>
+                  <c:v>13.985</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>79281</c:v>
+                  <c:v>14.287</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>80783</c:v>
+                  <c:v>14.588</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>82286</c:v>
+                  <c:v>14.89</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>83790</c:v>
+                  <c:v>15.194</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>85293</c:v>
+                  <c:v>15.496</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>86795</c:v>
+                  <c:v>15.798</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>88298</c:v>
+                  <c:v>16.099</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>89802</c:v>
+                  <c:v>16.401</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>91304</c:v>
+                  <c:v>16.706</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>92807</c:v>
+                  <c:v>17.008</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>94310</c:v>
+                  <c:v>17.31</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17.612</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17.914</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18.218</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>18.519</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>18.821</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>19.123</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>19.425</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19.728</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>20.03</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>20.333</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>20.635</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>20.937</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>21.241</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>21.543</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Results!$C$2:$C$59</c:f>
+              <c:f>Results!$C$3:$C$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="72"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>28</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>28</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>13</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>28</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>28</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>29</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>29</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>13</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>13</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>28</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>28</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>13</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>13</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>28</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>28</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>13</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>13</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>29</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>29</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>13</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>13</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>29</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>29</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>11</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>11</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>28</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>28</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>13</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>13</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>29</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>29</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>14</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>14</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>29</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>29</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>29</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>29</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>12</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>29</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>29</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>13</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>13</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>30</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>30</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>13</c:v>
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
         </c:ser>
-        <c:axId val="50010001"/>
-        <c:axId val="50010002"/>
+        <c:axId val="50010003"/>
+        <c:axId val="50010004"/>
       </c:scatterChart>
       <c:valAx>
         <c:axId val="50010001"/>
@@ -960,7 +1133,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Ambient ADC</a:t>
+                  <a:t>Ambient DC ADC</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -970,6 +1143,2129 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50010003"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
+        <c:crossAx val="50010004"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50010004"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Ambient AC ADC</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010003"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>I Active DC Readings</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>740nm</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="008000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Results!$A$3:$A$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>0.049</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.381</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.984</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.286</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.891</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.193</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.495</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.798</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.102</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.404</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.706</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.309</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.613</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.915</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.217000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.519</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.82</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.125</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.427</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.729</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.031000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.333</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.636</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.938</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.24</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.542</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.843999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9.147</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>9.449</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.752000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>10.054</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>10.356</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>10.66</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.961</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>11.263</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>11.565</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11.867</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>12.171</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12.472</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>12.774</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>13.076</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>13.379</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>13.683</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>13.985</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>14.287</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>14.588</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14.89</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>15.194</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>15.496</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.798</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>16.099</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16.401</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16.706</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>17.008</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>17.31</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17.612</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17.914</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18.218</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>18.519</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>18.821</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>19.123</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>19.425</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19.728</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>20.03</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>20.333</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>20.635</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>20.937</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>21.241</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>21.543</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Results!$D$3:$D$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>739</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>738</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>739</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>738</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>739</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>994</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>992</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>991</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>991</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>743</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>739</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>741</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>739</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>994</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>992</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>850nm</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Results!$A$3:$A$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>0.049</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.381</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.984</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.286</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.891</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.193</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.495</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.798</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.102</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.404</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.706</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.309</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.613</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.915</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.217000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.519</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.82</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.125</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.427</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.729</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.031000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.333</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.636</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.938</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.24</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.542</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.843999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9.147</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>9.449</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.752000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>10.054</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>10.356</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>10.66</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.961</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>11.263</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>11.565</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11.867</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>12.171</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12.472</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>12.774</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>13.076</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>13.379</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>13.683</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>13.985</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>14.287</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>14.588</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14.89</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>15.194</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>15.496</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.798</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>16.099</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16.401</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16.706</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>17.008</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>17.31</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17.612</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17.914</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18.218</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>18.519</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>18.821</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>19.123</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>19.425</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19.728</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>20.03</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>20.333</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>20.635</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>20.937</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>21.241</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>21.543</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Results!$F$3:$F$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>114</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>338</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>337</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>337</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>334</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>109</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50020001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50020002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>ADC</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Live AC Readings</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>740nm</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="008000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Results!$A$3:$A$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>0.049</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.381</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.984</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.286</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.891</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.193</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.495</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.798</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.102</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.404</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.706</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.309</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.613</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.915</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.217000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.519</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.82</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.125</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.427</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.729</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.031000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.333</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.636</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.938</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.24</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.542</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.843999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9.147</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>9.449</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.752000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>10.054</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>10.356</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>10.66</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.961</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>11.263</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>11.565</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11.867</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>12.171</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12.472</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>12.774</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>13.076</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>13.379</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>13.683</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>13.985</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>14.287</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>14.588</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14.89</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>15.194</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>15.496</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.798</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>16.099</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16.401</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16.706</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>17.008</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>17.31</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17.612</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17.914</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18.218</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>18.519</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>18.821</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>19.123</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>19.425</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19.728</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>20.03</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>20.333</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>20.635</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>20.937</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>21.241</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>21.543</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Results!$E$3:$E$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>850nm</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Results!$A$3:$A$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>0.049</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.381</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6820000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.984</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.286</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.891</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.193</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.495</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.798</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.102</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.404</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.706</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.007</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.309</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.613</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.915</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.217000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.519</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.82</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.125</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.427</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.729</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.031000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.333</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.636</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7.938</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.24</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.542</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.843999999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9.147</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>9.449</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>9.752000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>10.054</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>10.356</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>10.66</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.961</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>11.263</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>11.565</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11.867</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>12.171</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12.472</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>12.774</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>13.076</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>13.379</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>13.683</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>13.985</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>14.287</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>14.588</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14.89</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>15.194</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>15.496</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>15.798</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>16.099</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16.401</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16.706</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>17.008</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>17.31</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>17.612</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17.914</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18.218</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>18.519</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>18.821</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>19.123</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>19.425</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19.728</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>20.03</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>20.333</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>20.635</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>20.937</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>21.241</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>21.543</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Results!$G$3:$G$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="72"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50030001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50030002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>ADC</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1015,6 +3311,66 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1308,7 +3664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1345,7 +3701,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>10067</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1369,21 +3725,21 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-1</v>
+        <v>739.9400000000001</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>86.31</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>10115</v>
+        <v>0.049</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1403,19 +3759,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>11649</v>
+        <v>0.381</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>253</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1429,13 +3785,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>13150</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="B5">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1455,13 +3811,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>14652</v>
+        <v>0.984</v>
       </c>
       <c r="B6">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1470,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1481,13 +3837,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>16156</v>
+        <v>1.286</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>253</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1507,19 +3863,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>17660</v>
+        <v>1.59</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>253</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>739</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1533,19 +3889,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>19162</v>
+        <v>1.891</v>
       </c>
       <c r="B9">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="C9">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1559,25 +3915,25 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>20664</v>
+        <v>2.193</v>
       </c>
       <c r="B10">
-        <v>27</v>
+        <v>253</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>739</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1585,19 +3941,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>22168</v>
+        <v>2.495</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>253</v>
       </c>
       <c r="C11">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1611,19 +3967,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>23672</v>
+        <v>2.798</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>253</v>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>739</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1637,13 +3993,13 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
-        <v>25174</v>
+        <v>3.102</v>
       </c>
       <c r="B13">
-        <v>28</v>
+        <v>253</v>
       </c>
       <c r="C13">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1663,13 +4019,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
-        <v>26676</v>
+        <v>3.404</v>
       </c>
       <c r="B14">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="C14">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1678,10 +4034,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1689,13 +4045,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
-        <v>28180</v>
+        <v>3.706</v>
       </c>
       <c r="B15">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1715,19 +4071,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
-        <v>29683</v>
+        <v>4.007</v>
       </c>
       <c r="B16">
-        <v>12</v>
+        <v>251</v>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1741,13 +4097,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>31185</v>
+        <v>4.309</v>
       </c>
       <c r="B17">
-        <v>27</v>
+        <v>251</v>
       </c>
       <c r="C17">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1767,13 +4123,13 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>32688</v>
+        <v>4.613</v>
       </c>
       <c r="B18">
-        <v>27</v>
+        <v>251</v>
       </c>
       <c r="C18">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1782,10 +4138,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>-15</v>
+        <v>114</v>
       </c>
       <c r="G18">
-        <v>-17</v>
+        <v>12</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1793,13 +4149,13 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>34192</v>
+        <v>4.915</v>
       </c>
       <c r="B19">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1808,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1819,25 +4175,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>35695</v>
+        <v>5.217000000000001</v>
       </c>
       <c r="B20">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1845,13 +4201,13 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>37197</v>
+        <v>5.519</v>
       </c>
       <c r="B21">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C21">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1860,10 +4216,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1871,13 +4227,13 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>38700</v>
+        <v>5.82</v>
       </c>
       <c r="B22">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C22">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1886,10 +4242,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>-16</v>
+        <v>91</v>
       </c>
       <c r="G22">
-        <v>-15</v>
+        <v>12</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1897,19 +4253,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>40204</v>
+        <v>6.125</v>
       </c>
       <c r="B23">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>994</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1923,16 +4279,16 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>41707</v>
+        <v>6.427</v>
       </c>
       <c r="B24">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>990</v>
       </c>
       <c r="E24">
         <v>15</v>
@@ -1949,19 +4305,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>43209</v>
+        <v>6.729</v>
       </c>
       <c r="B25">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>992</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1975,25 +4331,25 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>44711</v>
+        <v>7.031000000000001</v>
       </c>
       <c r="B26">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F26">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2001,19 +4357,19 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>46216</v>
+        <v>7.333</v>
       </c>
       <c r="B27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2027,19 +4383,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>47719</v>
+        <v>7.636</v>
       </c>
       <c r="B28">
-        <v>12</v>
+        <v>251</v>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2053,13 +4409,13 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>49221</v>
+        <v>7.938</v>
       </c>
       <c r="B29">
-        <v>28</v>
+        <v>254</v>
       </c>
       <c r="C29">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -2079,13 +4435,13 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>50723</v>
+        <v>8.24</v>
       </c>
       <c r="B30">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C30">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2094,10 +4450,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2105,13 +4461,13 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>52228</v>
+        <v>8.542</v>
       </c>
       <c r="B31">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="C31">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2131,19 +4487,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>53731</v>
+        <v>8.843999999999999</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="C32">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2157,13 +4513,13 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>55233</v>
+        <v>9.147</v>
       </c>
       <c r="B33">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C33">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2172,10 +4528,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2183,13 +4539,13 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>56735</v>
+        <v>9.449</v>
       </c>
       <c r="B34">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C34">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2198,10 +4554,10 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>-16</v>
+        <v>98</v>
       </c>
       <c r="G34">
-        <v>-17</v>
+        <v>11</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2209,25 +4565,25 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>58240</v>
+        <v>9.752000000000001</v>
       </c>
       <c r="B35">
-        <v>12</v>
+        <v>251</v>
       </c>
       <c r="C35">
+        <v>6</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>96</v>
+      </c>
+      <c r="G35">
         <v>11</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2235,25 +4591,25 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>59743</v>
+        <v>10.054</v>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>251</v>
       </c>
       <c r="C36">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2261,13 +4617,13 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>61245</v>
+        <v>10.356</v>
       </c>
       <c r="B37">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C37">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2276,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2287,13 +4643,13 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>62747</v>
+        <v>10.66</v>
       </c>
       <c r="B38">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C38">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2302,10 +4658,10 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -2313,13 +4669,13 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>64251</v>
+        <v>10.961</v>
       </c>
       <c r="B39">
-        <v>12</v>
+        <v>253</v>
       </c>
       <c r="C39">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2339,19 +4695,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>65755</v>
+        <v>11.263</v>
       </c>
       <c r="B40">
-        <v>12</v>
+        <v>251</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2365,13 +4721,13 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>67257</v>
+        <v>11.565</v>
       </c>
       <c r="B41">
-        <v>29</v>
+        <v>253</v>
       </c>
       <c r="C41">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2391,13 +4747,13 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>68759</v>
+        <v>11.867</v>
       </c>
       <c r="B42">
-        <v>29</v>
+        <v>252</v>
       </c>
       <c r="C42">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2406,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2417,13 +4773,13 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>70263</v>
+        <v>12.171</v>
       </c>
       <c r="B43">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="C43">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2432,10 +4788,10 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2443,25 +4799,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>71767</v>
+        <v>12.472</v>
       </c>
       <c r="B44">
-        <v>13</v>
+        <v>252</v>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2469,13 +4825,13 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>73269</v>
+        <v>12.774</v>
       </c>
       <c r="B45">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="C45">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2484,10 +4840,10 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -2495,13 +4851,13 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>74771</v>
+        <v>13.076</v>
       </c>
       <c r="B46">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="C46">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2510,10 +4866,10 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>-8</v>
+        <v>90</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2521,25 +4877,25 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>76275</v>
+        <v>13.379</v>
       </c>
       <c r="B47">
+        <v>252</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>88</v>
+      </c>
+      <c r="G47">
         <v>12</v>
-      </c>
-      <c r="C47">
-        <v>12</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -2547,25 +4903,25 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>77778</v>
+        <v>13.683</v>
       </c>
       <c r="B48">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -2573,13 +4929,13 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>79281</v>
+        <v>13.985</v>
       </c>
       <c r="B49">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2588,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -2599,13 +4955,13 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>80783</v>
+        <v>14.287</v>
       </c>
       <c r="B50">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2614,10 +4970,10 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>-16</v>
+        <v>337</v>
       </c>
       <c r="G50">
-        <v>-29</v>
+        <v>17</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -2625,13 +4981,13 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>82286</v>
+        <v>14.588</v>
       </c>
       <c r="B51">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2640,10 +4996,10 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -2651,25 +5007,25 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>83790</v>
+        <v>14.89</v>
       </c>
       <c r="B52">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -2677,13 +5033,13 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>85293</v>
+        <v>15.194</v>
       </c>
       <c r="B53">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C53">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2703,13 +5059,13 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>86795</v>
+        <v>15.496</v>
       </c>
       <c r="B54">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="C54">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2718,10 +5074,10 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -2729,13 +5085,13 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>88298</v>
+        <v>15.798</v>
       </c>
       <c r="B55">
-        <v>12</v>
+        <v>252</v>
       </c>
       <c r="C55">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2755,19 +5111,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>89802</v>
+        <v>16.099</v>
       </c>
       <c r="B56">
-        <v>12</v>
+        <v>251</v>
       </c>
       <c r="C56">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D56">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2781,13 +5137,13 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>91304</v>
+        <v>16.401</v>
       </c>
       <c r="B57">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="C57">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2807,25 +5163,25 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>92807</v>
+        <v>16.706</v>
       </c>
       <c r="B58">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="C58">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>743</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F58">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -2833,19 +5189,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>94310</v>
+        <v>17.008</v>
       </c>
       <c r="B59">
+        <v>252</v>
+      </c>
+      <c r="C59">
+        <v>4</v>
+      </c>
+      <c r="D59">
+        <v>739</v>
+      </c>
+      <c r="E59">
         <v>12</v>
-      </c>
-      <c r="C59">
-        <v>13</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2859,27 +5215,417 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>95814</v>
+        <v>17.31</v>
       </c>
       <c r="B60">
+        <v>252</v>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60">
+        <v>741</v>
+      </c>
+      <c r="E60">
         <v>12</v>
       </c>
-      <c r="C60">
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>17.612</v>
+      </c>
+      <c r="B61">
+        <v>252</v>
+      </c>
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61">
+        <v>740</v>
+      </c>
+      <c r="E61">
+        <v>11</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>17.914</v>
+      </c>
+      <c r="B62">
+        <v>252</v>
+      </c>
+      <c r="C62">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>739</v>
+      </c>
+      <c r="E62">
+        <v>12</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>18.218</v>
+      </c>
+      <c r="B63">
+        <v>251</v>
+      </c>
+      <c r="C63">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>18.519</v>
+      </c>
+      <c r="B64">
+        <v>252</v>
+      </c>
+      <c r="C64">
+        <v>5</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>18.821</v>
+      </c>
+      <c r="B65">
+        <v>252</v>
+      </c>
+      <c r="C65">
+        <v>7</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>19.123</v>
+      </c>
+      <c r="B66">
+        <v>250</v>
+      </c>
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>19.425</v>
+      </c>
+      <c r="B67">
+        <v>250</v>
+      </c>
+      <c r="C67">
+        <v>5</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68">
+        <v>19.728</v>
+      </c>
+      <c r="B68">
+        <v>250</v>
+      </c>
+      <c r="C68">
+        <v>5</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>109</v>
+      </c>
+      <c r="G68">
         <v>13</v>
       </c>
-      <c r="D60">
-        <v>15</v>
-      </c>
-      <c r="E60">
-        <v>15</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69">
+        <v>20.03</v>
+      </c>
+      <c r="B69">
+        <v>250</v>
+      </c>
+      <c r="C69">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>99</v>
+      </c>
+      <c r="G69">
+        <v>12</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>20.333</v>
+      </c>
+      <c r="B70">
+        <v>250</v>
+      </c>
+      <c r="C70">
+        <v>5</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>96</v>
+      </c>
+      <c r="G70">
+        <v>11</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>20.635</v>
+      </c>
+      <c r="B71">
+        <v>250</v>
+      </c>
+      <c r="C71">
+        <v>5</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>92</v>
+      </c>
+      <c r="G71">
+        <v>11</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>20.937</v>
+      </c>
+      <c r="B72">
+        <v>250</v>
+      </c>
+      <c r="C72">
+        <v>5</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>92</v>
+      </c>
+      <c r="G72">
+        <v>11</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>21.241</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>994</v>
+      </c>
+      <c r="E73">
+        <v>16</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>21.543</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>992</v>
+      </c>
+      <c r="E74">
+        <v>16</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>21.844</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>991</v>
+      </c>
+      <c r="E75">
+        <v>16</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
         <v>0</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jennifer\Documents\GitHub\BME-499\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC54167-FB68-4D97-9AF2-CDC8E840D99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -49,8 +55,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,12 +119,30 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -136,12 +160,14 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -151,7 +177,7 @@
           <c:spPr>
             <a:ln>
               <a:solidFill>
-                <a:srgbClr val="0000FF"/>
+                <a:srgbClr val="008000"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -160,460 +186,463 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Results!$A$3:$A$74</c:f>
+              <c:f>Results!$A$3:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.049</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.381</c:v>
+                  <c:v>0.38300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6820000000000001</c:v>
+                  <c:v>0.68500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.984</c:v>
+                  <c:v>0.98699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.286</c:v>
+                  <c:v>1.2889999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.59</c:v>
+                  <c:v>1.5920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.891</c:v>
+                  <c:v>1.895</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.193</c:v>
+                  <c:v>2.1970000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.495</c:v>
+                  <c:v>2.4990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.798</c:v>
+                  <c:v>2.8010000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.102</c:v>
+                  <c:v>3.1059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.404</c:v>
+                  <c:v>3.4079999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.706</c:v>
+                  <c:v>3.7090000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.007</c:v>
+                  <c:v>4.0110000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.309</c:v>
+                  <c:v>4.3129999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.613</c:v>
+                  <c:v>4.617</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.915</c:v>
+                  <c:v>4.9189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.217000000000001</c:v>
+                  <c:v>5.2210000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.519</c:v>
+                  <c:v>5.5229999999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.82</c:v>
+                  <c:v>5.8250000000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6.125</c:v>
+                  <c:v>6.1289999999999996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.427</c:v>
+                  <c:v>6.4320000000000004</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.729</c:v>
+                  <c:v>6.734</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.031000000000001</c:v>
+                  <c:v>7.0359999999999996</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.333</c:v>
+                  <c:v>7.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.636</c:v>
+                  <c:v>7.641</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.938</c:v>
+                  <c:v>7.944</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.24</c:v>
+                  <c:v>8.2460000000000004</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>8.542</c:v>
+                  <c:v>8.548</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8.843999999999999</c:v>
+                  <c:v>8.85</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.147</c:v>
+                  <c:v>9.1539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9.449</c:v>
+                  <c:v>9.4559999999999995</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.752000000000001</c:v>
+                  <c:v>9.7569999999999997</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10.054</c:v>
+                  <c:v>10.06</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10.356</c:v>
+                  <c:v>10.362</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10.66</c:v>
+                  <c:v>10.666</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10.961</c:v>
+                  <c:v>10.968</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>11.263</c:v>
+                  <c:v>11.27</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>11.565</c:v>
+                  <c:v>11.571999999999999</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>11.867</c:v>
+                  <c:v>11.874000000000001</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>12.171</c:v>
+                  <c:v>12.178000000000001</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12.472</c:v>
+                  <c:v>12.48</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>12.774</c:v>
+                  <c:v>12.782</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>13.076</c:v>
+                  <c:v>13.084</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>13.379</c:v>
+                  <c:v>13.387</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>13.683</c:v>
+                  <c:v>13.691000000000001</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>13.985</c:v>
+                  <c:v>13.993</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>14.287</c:v>
+                  <c:v>14.295</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>14.588</c:v>
+                  <c:v>14.597</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>14.89</c:v>
+                  <c:v>14.898999999999999</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>15.194</c:v>
+                  <c:v>15.202999999999999</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>15.496</c:v>
+                  <c:v>15.505000000000001</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>15.798</c:v>
+                  <c:v>15.805999999999999</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>16.099</c:v>
+                  <c:v>16.108000000000001</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>16.401</c:v>
+                  <c:v>16.41</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>16.706</c:v>
+                  <c:v>16.715</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>17.008</c:v>
+                  <c:v>17.016999999999999</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>17.31</c:v>
+                  <c:v>17.318999999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>17.612</c:v>
+                  <c:v>17.620999999999999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>17.914</c:v>
+                  <c:v>17.922999999999998</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>18.218</c:v>
+                  <c:v>18.227</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>18.519</c:v>
+                  <c:v>18.529</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>18.821</c:v>
+                  <c:v>18.831</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>19.123</c:v>
+                  <c:v>19.132999999999999</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>19.425</c:v>
+                  <c:v>19.434999999999999</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>19.728</c:v>
+                  <c:v>19.739000000000001</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>20.03</c:v>
+                  <c:v>20.042000000000002</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>20.333</c:v>
+                  <c:v>20.344000000000001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>20.635</c:v>
+                  <c:v>20.646000000000001</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>20.937</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>21.241</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>21.543</c:v>
+                  <c:v>20.948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Results!$B$3:$B$74</c:f>
+              <c:f>Results!$B$3:$B$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>253</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>253</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>253</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>253</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>253</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>253</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>253</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>253</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>254</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>251</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>251</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>251</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>253</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>253</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>252</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>252</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>252</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>252</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>252</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>251</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>251</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>252</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>252</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>250</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>250</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>250</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>250</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>250</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>250</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>250</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FE1D-4F02-91D8-A32B2E496C17}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:scatterChart>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -621,11 +650,10 @@
             <c:v>AmbientAC</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
             </a:ln>
           </c:spPr>
           <c:marker>
@@ -633,455 +661,457 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Results!$A$3:$A$74</c:f>
+              <c:f>Results!$A$3:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.049</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.381</c:v>
+                  <c:v>0.38300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6820000000000001</c:v>
+                  <c:v>0.68500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.984</c:v>
+                  <c:v>0.98699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.286</c:v>
+                  <c:v>1.2889999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.59</c:v>
+                  <c:v>1.5920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.891</c:v>
+                  <c:v>1.895</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.193</c:v>
+                  <c:v>2.1970000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.495</c:v>
+                  <c:v>2.4990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.798</c:v>
+                  <c:v>2.8010000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.102</c:v>
+                  <c:v>3.1059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.404</c:v>
+                  <c:v>3.4079999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.706</c:v>
+                  <c:v>3.7090000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.007</c:v>
+                  <c:v>4.0110000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.309</c:v>
+                  <c:v>4.3129999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.613</c:v>
+                  <c:v>4.617</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.915</c:v>
+                  <c:v>4.9189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.217000000000001</c:v>
+                  <c:v>5.2210000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.519</c:v>
+                  <c:v>5.5229999999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.82</c:v>
+                  <c:v>5.8250000000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6.125</c:v>
+                  <c:v>6.1289999999999996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.427</c:v>
+                  <c:v>6.4320000000000004</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.729</c:v>
+                  <c:v>6.734</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.031000000000001</c:v>
+                  <c:v>7.0359999999999996</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.333</c:v>
+                  <c:v>7.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.636</c:v>
+                  <c:v>7.641</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.938</c:v>
+                  <c:v>7.944</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.24</c:v>
+                  <c:v>8.2460000000000004</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>8.542</c:v>
+                  <c:v>8.548</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8.843999999999999</c:v>
+                  <c:v>8.85</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.147</c:v>
+                  <c:v>9.1539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9.449</c:v>
+                  <c:v>9.4559999999999995</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.752000000000001</c:v>
+                  <c:v>9.7569999999999997</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10.054</c:v>
+                  <c:v>10.06</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10.356</c:v>
+                  <c:v>10.362</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10.66</c:v>
+                  <c:v>10.666</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10.961</c:v>
+                  <c:v>10.968</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>11.263</c:v>
+                  <c:v>11.27</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>11.565</c:v>
+                  <c:v>11.571999999999999</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>11.867</c:v>
+                  <c:v>11.874000000000001</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>12.171</c:v>
+                  <c:v>12.178000000000001</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12.472</c:v>
+                  <c:v>12.48</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>12.774</c:v>
+                  <c:v>12.782</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>13.076</c:v>
+                  <c:v>13.084</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>13.379</c:v>
+                  <c:v>13.387</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>13.683</c:v>
+                  <c:v>13.691000000000001</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>13.985</c:v>
+                  <c:v>13.993</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>14.287</c:v>
+                  <c:v>14.295</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>14.588</c:v>
+                  <c:v>14.597</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>14.89</c:v>
+                  <c:v>14.898999999999999</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>15.194</c:v>
+                  <c:v>15.202999999999999</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>15.496</c:v>
+                  <c:v>15.505000000000001</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>15.798</c:v>
+                  <c:v>15.805999999999999</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>16.099</c:v>
+                  <c:v>16.108000000000001</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>16.401</c:v>
+                  <c:v>16.41</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>16.706</c:v>
+                  <c:v>16.715</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>17.008</c:v>
+                  <c:v>17.016999999999999</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>17.31</c:v>
+                  <c:v>17.318999999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>17.612</c:v>
+                  <c:v>17.620999999999999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>17.914</c:v>
+                  <c:v>17.922999999999998</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>18.218</c:v>
+                  <c:v>18.227</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>18.519</c:v>
+                  <c:v>18.529</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>18.821</c:v>
+                  <c:v>18.831</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>19.123</c:v>
+                  <c:v>19.132999999999999</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>19.425</c:v>
+                  <c:v>19.434999999999999</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>19.728</c:v>
+                  <c:v>19.739000000000001</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>20.03</c:v>
+                  <c:v>20.042000000000002</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>20.333</c:v>
+                  <c:v>20.344000000000001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>20.635</c:v>
+                  <c:v>20.646000000000001</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>20.937</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>21.241</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>21.543</c:v>
+                  <c:v>20.948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Results!$C$3:$C$74</c:f>
+              <c:f>Results!$C$3:$C$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>6</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>6</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>6</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>5</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>5</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>4</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>5</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>4</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>4</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>4</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>4</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>4</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>7</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>5</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FE1D-4F02-91D8-A32B2E496C17}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="50010003"/>
         <c:axId val="50010004"/>
       </c:scatterChart>
@@ -1090,6 +1120,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1107,9 +1138,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
@@ -1120,6 +1153,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -1138,9 +1172,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -1154,6 +1190,8 @@
         <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="none"/>
         <c:crossAx val="50010004"/>
         <c:crosses val="autoZero"/>
@@ -1164,6 +1202,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="r"/>
         <c:title>
           <c:tx>
@@ -1181,9 +1220,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010003"/>
         <c:crosses val="max"/>
@@ -1192,9 +1233,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1205,8 +1248,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1224,12 +1277,14 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1248,235 +1303,232 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Results!$A$3:$A$74</c:f>
+              <c:f>Results!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
-                  <c:v>0.049</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.381</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6820000000000001</c:v>
+                  <c:v>0.38300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.984</c:v>
+                  <c:v>0.68500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.286</c:v>
+                  <c:v>0.98699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.59</c:v>
+                  <c:v>1.2889999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.891</c:v>
+                  <c:v>1.5920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.193</c:v>
+                  <c:v>1.895</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.495</c:v>
+                  <c:v>2.1970000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.798</c:v>
+                  <c:v>2.4990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.102</c:v>
+                  <c:v>2.8010000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.404</c:v>
+                  <c:v>3.1059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.706</c:v>
+                  <c:v>3.4079999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.007</c:v>
+                  <c:v>3.7090000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.309</c:v>
+                  <c:v>4.0110000000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.613</c:v>
+                  <c:v>4.3129999999999997</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.915</c:v>
+                  <c:v>4.617</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.217000000000001</c:v>
+                  <c:v>4.9189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.519</c:v>
+                  <c:v>5.2210000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.82</c:v>
+                  <c:v>5.5229999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6.125</c:v>
+                  <c:v>5.8250000000000002</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.427</c:v>
+                  <c:v>6.1289999999999996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.729</c:v>
+                  <c:v>6.4320000000000004</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.031000000000001</c:v>
+                  <c:v>6.734</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.333</c:v>
+                  <c:v>7.0359999999999996</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.636</c:v>
+                  <c:v>7.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.938</c:v>
+                  <c:v>7.641</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.24</c:v>
+                  <c:v>7.944</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>8.542</c:v>
+                  <c:v>8.2460000000000004</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8.843999999999999</c:v>
+                  <c:v>8.548</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.147</c:v>
+                  <c:v>8.85</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9.449</c:v>
+                  <c:v>9.1539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.752000000000001</c:v>
+                  <c:v>9.4559999999999995</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10.054</c:v>
+                  <c:v>9.7569999999999997</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10.356</c:v>
+                  <c:v>10.06</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10.66</c:v>
+                  <c:v>10.362</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10.961</c:v>
+                  <c:v>10.666</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>11.263</c:v>
+                  <c:v>10.968</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>11.565</c:v>
+                  <c:v>11.27</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>11.867</c:v>
+                  <c:v>11.571999999999999</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>12.171</c:v>
+                  <c:v>11.874000000000001</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12.472</c:v>
+                  <c:v>12.178000000000001</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>12.774</c:v>
+                  <c:v>12.48</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>13.076</c:v>
+                  <c:v>12.782</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>13.379</c:v>
+                  <c:v>13.084</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>13.683</c:v>
+                  <c:v>13.387</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>13.985</c:v>
+                  <c:v>13.691000000000001</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>14.287</c:v>
+                  <c:v>13.993</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>14.588</c:v>
+                  <c:v>14.295</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>14.89</c:v>
+                  <c:v>14.597</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>15.194</c:v>
+                  <c:v>14.898999999999999</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>15.496</c:v>
+                  <c:v>15.202999999999999</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>15.798</c:v>
+                  <c:v>15.505000000000001</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>16.099</c:v>
+                  <c:v>15.805999999999999</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>16.401</c:v>
+                  <c:v>16.108000000000001</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>16.706</c:v>
+                  <c:v>16.41</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>17.008</c:v>
+                  <c:v>16.715</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>17.31</c:v>
+                  <c:v>17.016999999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>17.612</c:v>
+                  <c:v>17.318999999999999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>17.914</c:v>
+                  <c:v>17.620999999999999</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>18.218</c:v>
+                  <c:v>17.922999999999998</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>18.519</c:v>
+                  <c:v>18.227</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>18.821</c:v>
+                  <c:v>18.529</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>19.123</c:v>
+                  <c:v>18.831</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>19.425</c:v>
+                  <c:v>19.132999999999999</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>19.728</c:v>
+                  <c:v>19.434999999999999</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>20.03</c:v>
+                  <c:v>19.739000000000001</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>20.333</c:v>
+                  <c:v>20.042000000000002</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>20.635</c:v>
+                  <c:v>20.344000000000001</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>20.937</c:v>
+                  <c:v>20.646000000000001</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>21.241</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>21.543</c:v>
+                  <c:v>20.948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Results!$D$3:$D$74</c:f>
+              <c:f>Results!$D$2:$D$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1493,22 +1545,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>739</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>738</c:v>
+                  <c:v>854</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>739</c:v>
+                  <c:v>852</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>738</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>739</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -1538,37 +1590,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>994</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>990</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>992</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>991</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>991</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>854</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0</c:v>
+                  <c:v>849</c:v>
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0</c:v>
@@ -1616,19 +1668,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0</c:v>
+                  <c:v>855</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0</c:v>
+                  <c:v>853</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0</c:v>
@@ -1643,19 +1695,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>743</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>739</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>741</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>740</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>739</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0</c:v>
@@ -1676,26 +1728,29 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0</c:v>
+                  <c:v>855</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0</c:v>
+                  <c:v>852</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0</c:v>
+                  <c:v>852</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>994</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>992</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2D9C-40DA-9FD9-1C3E18130E47}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1704,11 +1759,10 @@
             <c:v>850nm</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
             </a:ln>
           </c:spPr>
           <c:marker>
@@ -1716,235 +1770,232 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Results!$A$3:$A$74</c:f>
+              <c:f>Results!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
-                  <c:v>0.049</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.381</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6820000000000001</c:v>
+                  <c:v>0.38300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.984</c:v>
+                  <c:v>0.68500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.286</c:v>
+                  <c:v>0.98699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.59</c:v>
+                  <c:v>1.2889999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.891</c:v>
+                  <c:v>1.5920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.193</c:v>
+                  <c:v>1.895</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.495</c:v>
+                  <c:v>2.1970000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.798</c:v>
+                  <c:v>2.4990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.102</c:v>
+                  <c:v>2.8010000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.404</c:v>
+                  <c:v>3.1059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.706</c:v>
+                  <c:v>3.4079999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.007</c:v>
+                  <c:v>3.7090000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.309</c:v>
+                  <c:v>4.0110000000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.613</c:v>
+                  <c:v>4.3129999999999997</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.915</c:v>
+                  <c:v>4.617</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.217000000000001</c:v>
+                  <c:v>4.9189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.519</c:v>
+                  <c:v>5.2210000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.82</c:v>
+                  <c:v>5.5229999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6.125</c:v>
+                  <c:v>5.8250000000000002</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.427</c:v>
+                  <c:v>6.1289999999999996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.729</c:v>
+                  <c:v>6.4320000000000004</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.031000000000001</c:v>
+                  <c:v>6.734</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.333</c:v>
+                  <c:v>7.0359999999999996</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.636</c:v>
+                  <c:v>7.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.938</c:v>
+                  <c:v>7.641</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.24</c:v>
+                  <c:v>7.944</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>8.542</c:v>
+                  <c:v>8.2460000000000004</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8.843999999999999</c:v>
+                  <c:v>8.548</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.147</c:v>
+                  <c:v>8.85</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9.449</c:v>
+                  <c:v>9.1539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.752000000000001</c:v>
+                  <c:v>9.4559999999999995</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10.054</c:v>
+                  <c:v>9.7569999999999997</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10.356</c:v>
+                  <c:v>10.06</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10.66</c:v>
+                  <c:v>10.362</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10.961</c:v>
+                  <c:v>10.666</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>11.263</c:v>
+                  <c:v>10.968</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>11.565</c:v>
+                  <c:v>11.27</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>11.867</c:v>
+                  <c:v>11.571999999999999</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>12.171</c:v>
+                  <c:v>11.874000000000001</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12.472</c:v>
+                  <c:v>12.178000000000001</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>12.774</c:v>
+                  <c:v>12.48</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>13.076</c:v>
+                  <c:v>12.782</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>13.379</c:v>
+                  <c:v>13.084</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>13.683</c:v>
+                  <c:v>13.387</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>13.985</c:v>
+                  <c:v>13.691000000000001</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>14.287</c:v>
+                  <c:v>13.993</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>14.588</c:v>
+                  <c:v>14.295</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>14.89</c:v>
+                  <c:v>14.597</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>15.194</c:v>
+                  <c:v>14.898999999999999</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>15.496</c:v>
+                  <c:v>15.202999999999999</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>15.798</c:v>
+                  <c:v>15.505000000000001</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>16.099</c:v>
+                  <c:v>15.805999999999999</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>16.401</c:v>
+                  <c:v>16.108000000000001</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>16.706</c:v>
+                  <c:v>16.41</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>17.008</c:v>
+                  <c:v>16.715</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>17.31</c:v>
+                  <c:v>17.016999999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>17.612</c:v>
+                  <c:v>17.318999999999999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>17.914</c:v>
+                  <c:v>17.620999999999999</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>18.218</c:v>
+                  <c:v>17.922999999999998</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>18.519</c:v>
+                  <c:v>18.227</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>18.821</c:v>
+                  <c:v>18.529</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>19.123</c:v>
+                  <c:v>18.831</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>19.425</c:v>
+                  <c:v>19.132999999999999</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>19.728</c:v>
+                  <c:v>19.434999999999999</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>20.03</c:v>
+                  <c:v>19.739000000000001</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>20.333</c:v>
+                  <c:v>20.042000000000002</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>20.635</c:v>
+                  <c:v>20.344000000000001</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>20.937</c:v>
+                  <c:v>20.646000000000001</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>21.241</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>21.543</c:v>
+                  <c:v>20.948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Results!$F$3:$F$74</c:f>
+              <c:f>Results!$F$2:$F$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1991,22 +2042,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>114</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>95</c:v>
+                  <c:v>249</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>96</c:v>
+                  <c:v>187</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>94</c:v>
+                  <c:v>183</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>91</c:v>
+                  <c:v>191</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -2036,64 +2087,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>108</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>98</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>96</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>93</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>92</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>241</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0</c:v>
+                  <c:v>183</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0</c:v>
+                  <c:v>184</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0</c:v>
+                  <c:v>196</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>109</c:v>
+                  <c:v>208</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>95</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>92</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>90</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>88</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>338</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>337</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>337</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>335</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>334</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0</c:v>
@@ -2114,19 +2165,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0</c:v>
+                  <c:v>237</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0</c:v>
+                  <c:v>181</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0</c:v>
+                  <c:v>186</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0</c:v>
+                  <c:v>202</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0</c:v>
+                  <c:v>211</c:v>
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0</c:v>
@@ -2141,30 +2192,41 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>109</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>99</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>96</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>92</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>92</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="71">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2D9C-40DA-9FD9-1C3E18130E47}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:scatterChart>
@@ -2173,6 +2235,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -2190,9 +2253,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
@@ -2203,6 +2268,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -2221,9 +2287,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -2232,9 +2300,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -2245,8 +2315,18 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2264,12 +2344,14 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -2288,235 +2370,232 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Results!$A$3:$A$74</c:f>
+              <c:f>Results!$A$2:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
-                  <c:v>0.049</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.381</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6820000000000001</c:v>
+                  <c:v>0.38300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.984</c:v>
+                  <c:v>0.68500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.286</c:v>
+                  <c:v>0.98699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.59</c:v>
+                  <c:v>1.2889999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.891</c:v>
+                  <c:v>1.5920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.193</c:v>
+                  <c:v>1.895</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.495</c:v>
+                  <c:v>2.1970000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.798</c:v>
+                  <c:v>2.4990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.102</c:v>
+                  <c:v>2.8010000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.404</c:v>
+                  <c:v>3.1059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.706</c:v>
+                  <c:v>3.4079999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.007</c:v>
+                  <c:v>3.7090000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.309</c:v>
+                  <c:v>4.0110000000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.613</c:v>
+                  <c:v>4.3129999999999997</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.915</c:v>
+                  <c:v>4.617</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.217000000000001</c:v>
+                  <c:v>4.9189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.519</c:v>
+                  <c:v>5.2210000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.82</c:v>
+                  <c:v>5.5229999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6.125</c:v>
+                  <c:v>5.8250000000000002</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.427</c:v>
+                  <c:v>6.1289999999999996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.729</c:v>
+                  <c:v>6.4320000000000004</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.031000000000001</c:v>
+                  <c:v>6.734</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.333</c:v>
+                  <c:v>7.0359999999999996</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.636</c:v>
+                  <c:v>7.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.938</c:v>
+                  <c:v>7.641</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.24</c:v>
+                  <c:v>7.944</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>8.542</c:v>
+                  <c:v>8.2460000000000004</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8.843999999999999</c:v>
+                  <c:v>8.548</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.147</c:v>
+                  <c:v>8.85</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9.449</c:v>
+                  <c:v>9.1539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.752000000000001</c:v>
+                  <c:v>9.4559999999999995</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10.054</c:v>
+                  <c:v>9.7569999999999997</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10.356</c:v>
+                  <c:v>10.06</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10.66</c:v>
+                  <c:v>10.362</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10.961</c:v>
+                  <c:v>10.666</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>11.263</c:v>
+                  <c:v>10.968</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>11.565</c:v>
+                  <c:v>11.27</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>11.867</c:v>
+                  <c:v>11.571999999999999</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>12.171</c:v>
+                  <c:v>11.874000000000001</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12.472</c:v>
+                  <c:v>12.178000000000001</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>12.774</c:v>
+                  <c:v>12.48</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>13.076</c:v>
+                  <c:v>12.782</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>13.379</c:v>
+                  <c:v>13.084</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>13.683</c:v>
+                  <c:v>13.387</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>13.985</c:v>
+                  <c:v>13.691000000000001</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>14.287</c:v>
+                  <c:v>13.993</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>14.588</c:v>
+                  <c:v>14.295</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>14.89</c:v>
+                  <c:v>14.597</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>15.194</c:v>
+                  <c:v>14.898999999999999</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>15.496</c:v>
+                  <c:v>15.202999999999999</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>15.798</c:v>
+                  <c:v>15.505000000000001</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>16.099</c:v>
+                  <c:v>15.805999999999999</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>16.401</c:v>
+                  <c:v>16.108000000000001</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>16.706</c:v>
+                  <c:v>16.41</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>17.008</c:v>
+                  <c:v>16.715</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>17.31</c:v>
+                  <c:v>17.016999999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>17.612</c:v>
+                  <c:v>17.318999999999999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>17.914</c:v>
+                  <c:v>17.620999999999999</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>18.218</c:v>
+                  <c:v>17.922999999999998</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>18.519</c:v>
+                  <c:v>18.227</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>18.821</c:v>
+                  <c:v>18.529</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>19.123</c:v>
+                  <c:v>18.831</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>19.425</c:v>
+                  <c:v>19.132999999999999</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>19.728</c:v>
+                  <c:v>19.434999999999999</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>20.03</c:v>
+                  <c:v>19.739000000000001</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>20.333</c:v>
+                  <c:v>20.042000000000002</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>20.635</c:v>
+                  <c:v>20.344000000000001</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>20.937</c:v>
+                  <c:v>20.646000000000001</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>21.241</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>21.543</c:v>
+                  <c:v>20.948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Results!$E$3:$E$74</c:f>
+              <c:f>Results!$E$2:$E$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="71"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2533,22 +2612,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10</c:v>
+                  <c:v>855</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9</c:v>
+                  <c:v>853</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -2578,37 +2657,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>15</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>15</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>16</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>16</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>15</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>855</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>853</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>0</c:v>
@@ -2656,19 +2735,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0</c:v>
+                  <c:v>857</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0</c:v>
+                  <c:v>853</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0</c:v>
+                  <c:v>854</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0</c:v>
+                  <c:v>853</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0</c:v>
+                  <c:v>854</c:v>
                 </c:pt>
                 <c:pt idx="51">
                   <c:v>0</c:v>
@@ -2683,19 +2762,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0</c:v>
@@ -2716,26 +2795,29 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0</c:v>
+                  <c:v>855</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0</c:v>
+                  <c:v>851</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0</c:v>
+                  <c:v>852</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0</c:v>
+                  <c:v>852</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>16</c:v>
+                  <c:v>853</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4C3A-45AB-B117-9F8E7FA6BC5A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2744,11 +2826,10 @@
             <c:v>850nm</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
             </a:ln>
           </c:spPr>
           <c:marker>
@@ -2756,235 +2837,229 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Results!$A$3:$A$74</c:f>
+              <c:f>Results!$A$3:$A$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>0.049</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.381</c:v>
+                  <c:v>0.38300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6820000000000001</c:v>
+                  <c:v>0.68500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.984</c:v>
+                  <c:v>0.98699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.286</c:v>
+                  <c:v>1.2889999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.59</c:v>
+                  <c:v>1.5920000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.891</c:v>
+                  <c:v>1.895</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.193</c:v>
+                  <c:v>2.1970000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.495</c:v>
+                  <c:v>2.4990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.798</c:v>
+                  <c:v>2.8010000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.102</c:v>
+                  <c:v>3.1059999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.404</c:v>
+                  <c:v>3.4079999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.706</c:v>
+                  <c:v>3.7090000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.007</c:v>
+                  <c:v>4.0110000000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.309</c:v>
+                  <c:v>4.3129999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.613</c:v>
+                  <c:v>4.617</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.915</c:v>
+                  <c:v>4.9189999999999996</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.217000000000001</c:v>
+                  <c:v>5.2210000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.519</c:v>
+                  <c:v>5.5229999999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.82</c:v>
+                  <c:v>5.8250000000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>6.125</c:v>
+                  <c:v>6.1289999999999996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>6.427</c:v>
+                  <c:v>6.4320000000000004</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.729</c:v>
+                  <c:v>6.734</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.031000000000001</c:v>
+                  <c:v>7.0359999999999996</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7.333</c:v>
+                  <c:v>7.3380000000000001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.636</c:v>
+                  <c:v>7.641</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>7.938</c:v>
+                  <c:v>7.944</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.24</c:v>
+                  <c:v>8.2460000000000004</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>8.542</c:v>
+                  <c:v>8.548</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8.843999999999999</c:v>
+                  <c:v>8.85</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.147</c:v>
+                  <c:v>9.1539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9.449</c:v>
+                  <c:v>9.4559999999999995</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.752000000000001</c:v>
+                  <c:v>9.7569999999999997</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10.054</c:v>
+                  <c:v>10.06</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10.356</c:v>
+                  <c:v>10.362</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10.66</c:v>
+                  <c:v>10.666</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10.961</c:v>
+                  <c:v>10.968</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>11.263</c:v>
+                  <c:v>11.27</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>11.565</c:v>
+                  <c:v>11.571999999999999</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>11.867</c:v>
+                  <c:v>11.874000000000001</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>12.171</c:v>
+                  <c:v>12.178000000000001</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12.472</c:v>
+                  <c:v>12.48</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>12.774</c:v>
+                  <c:v>12.782</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>13.076</c:v>
+                  <c:v>13.084</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>13.379</c:v>
+                  <c:v>13.387</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>13.683</c:v>
+                  <c:v>13.691000000000001</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>13.985</c:v>
+                  <c:v>13.993</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>14.287</c:v>
+                  <c:v>14.295</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>14.588</c:v>
+                  <c:v>14.597</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>14.89</c:v>
+                  <c:v>14.898999999999999</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>15.194</c:v>
+                  <c:v>15.202999999999999</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>15.496</c:v>
+                  <c:v>15.505000000000001</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>15.798</c:v>
+                  <c:v>15.805999999999999</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>16.099</c:v>
+                  <c:v>16.108000000000001</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>16.401</c:v>
+                  <c:v>16.41</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>16.706</c:v>
+                  <c:v>16.715</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>17.008</c:v>
+                  <c:v>17.016999999999999</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>17.31</c:v>
+                  <c:v>17.318999999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>17.612</c:v>
+                  <c:v>17.620999999999999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>17.914</c:v>
+                  <c:v>17.922999999999998</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>18.218</c:v>
+                  <c:v>18.227</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>18.519</c:v>
+                  <c:v>18.529</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>18.821</c:v>
+                  <c:v>18.831</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>19.123</c:v>
+                  <c:v>19.132999999999999</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>19.425</c:v>
+                  <c:v>19.434999999999999</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>19.728</c:v>
+                  <c:v>19.739000000000001</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>20.03</c:v>
+                  <c:v>20.042000000000002</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>20.333</c:v>
+                  <c:v>20.344000000000001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>20.635</c:v>
+                  <c:v>20.646000000000001</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>20.937</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>21.241</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>21.543</c:v>
+                  <c:v>20.948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Results!$G$3:$G$74</c:f>
+              <c:f>Results!$G$3:$G$72</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="72"/>
+                <c:ptCount val="70"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3031,19 +3106,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12</c:v>
+                  <c:v>246</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12</c:v>
+                  <c:v>187</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>12</c:v>
+                  <c:v>184</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>12</c:v>
+                  <c:v>192</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>12</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -3076,64 +3151,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0</c:v>
+                  <c:v>185</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0</c:v>
+                  <c:v>186</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0</c:v>
+                  <c:v>197</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0</c:v>
+                  <c:v>209</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>13</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>17</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>18</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>17</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>16</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>17</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>0</c:v>
@@ -3151,19 +3226,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0</c:v>
+                  <c:v>236</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0</c:v>
+                  <c:v>182</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0</c:v>
+                  <c:v>189</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0</c:v>
+                  <c:v>203</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0</c:v>
+                  <c:v>211</c:v>
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>0</c:v>
@@ -3181,30 +3256,38 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>13</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>12</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>11</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="71">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4C3A-45AB-B117-9F8E7FA6BC5A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
       </c:scatterChart>
@@ -3213,6 +3296,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -3230,9 +3314,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030002"/>
         <c:crosses val="autoZero"/>
@@ -3243,6 +3329,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -3261,9 +3348,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -3272,9 +3361,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -3301,7 +3392,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3331,7 +3428,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3361,7 +3464,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3380,9 +3489,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3420,7 +3529,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3454,6 +3563,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3488,9 +3598,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3663,11 +3774,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J75"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J73"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3699,7 +3810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3725,21 +3836,21 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>739.9400000000001</v>
+        <v>850.06</v>
       </c>
       <c r="J2">
-        <v>86.31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>209.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="B3">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3757,15 +3868,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>0.381</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="B4">
-        <v>253</v>
+        <v>119</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -3783,15 +3894,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>0.6820000000000001</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="B5">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -3809,15 +3920,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>0.984</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="B6">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3835,15 +3946,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>1.286</v>
+        <v>1.2889999999999999</v>
       </c>
       <c r="B7">
-        <v>253</v>
+        <v>120</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3861,21 +3972,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>1.59</v>
+        <v>1.5920000000000001</v>
       </c>
       <c r="B8">
-        <v>253</v>
+        <v>120</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D8">
-        <v>739</v>
+        <v>854</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>855</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -3887,21 +3998,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>1.891</v>
+        <v>1.895</v>
       </c>
       <c r="B9">
-        <v>253</v>
+        <v>120</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D9">
-        <v>738</v>
+        <v>852</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>853</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -3913,21 +4024,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>2.193</v>
+        <v>2.1970000000000001</v>
       </c>
       <c r="B10">
-        <v>253</v>
+        <v>120</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D10">
-        <v>739</v>
+        <v>851</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>851</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -3939,21 +4050,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>2.495</v>
+        <v>2.4990000000000001</v>
       </c>
       <c r="B11">
-        <v>253</v>
+        <v>120</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D11">
-        <v>738</v>
+        <v>850</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>850</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -3965,21 +4076,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>2.798</v>
+        <v>2.8010000000000002</v>
       </c>
       <c r="B12">
-        <v>253</v>
+        <v>120</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D12">
-        <v>739</v>
+        <v>850</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>850</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -3991,15 +4102,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>3.102</v>
+        <v>3.1059999999999999</v>
       </c>
       <c r="B13">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4017,15 +4128,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>3.404</v>
+        <v>3.4079999999999999</v>
       </c>
       <c r="B14">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4043,15 +4154,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>3.706</v>
+        <v>3.7090000000000001</v>
       </c>
       <c r="B15">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4069,15 +4180,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>4.007</v>
+        <v>4.0110000000000001</v>
       </c>
       <c r="B16">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -4095,15 +4206,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>4.309</v>
+        <v>4.3129999999999997</v>
       </c>
       <c r="B17">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -4121,15 +4232,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>4.613</v>
+        <v>4.617</v>
       </c>
       <c r="B18">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -4138,24 +4249,24 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="G18">
-        <v>12</v>
+        <v>246</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>4.915</v>
+        <v>4.9189999999999996</v>
       </c>
       <c r="B19">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -4164,24 +4275,24 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="G19">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>5.217000000000001</v>
+        <v>5.2210000000000001</v>
       </c>
       <c r="B20">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4190,24 +4301,24 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="G20">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>5.519</v>
+        <v>5.5229999999999997</v>
       </c>
       <c r="B21">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4216,24 +4327,24 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>94</v>
+        <v>191</v>
       </c>
       <c r="G21">
-        <v>12</v>
+        <v>192</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>5.82</v>
+        <v>5.8250000000000002</v>
       </c>
       <c r="B22">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4242,30 +4353,30 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>91</v>
+        <v>205</v>
       </c>
       <c r="G22">
-        <v>12</v>
+        <v>204</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>6.125</v>
+        <v>6.1289999999999996</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D23">
-        <v>994</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -4277,21 +4388,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>6.427</v>
+        <v>6.4320000000000004</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D24">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -4303,21 +4414,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>6.729</v>
+        <v>6.734</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D25">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -4329,21 +4440,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>7.031000000000001</v>
+        <v>7.0359999999999996</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D26">
-        <v>991</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -4355,21 +4466,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>7.333</v>
+        <v>7.3380000000000001</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="D27">
-        <v>991</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -4381,21 +4492,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>7.636</v>
+        <v>7.641</v>
       </c>
       <c r="B28">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>854</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -4407,21 +4518,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>7.938</v>
+        <v>7.944</v>
       </c>
       <c r="B29">
-        <v>254</v>
+        <v>120</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -4433,21 +4544,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>8.24</v>
+        <v>8.2460000000000004</v>
       </c>
       <c r="B30">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -4459,21 +4570,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>8.542</v>
+        <v>8.548</v>
       </c>
       <c r="B31">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -4485,21 +4596,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>8.843999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="B32">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -4511,15 +4622,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>9.147</v>
+        <v>9.1539999999999999</v>
       </c>
       <c r="B33">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -4528,24 +4639,24 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>9.449</v>
+        <v>9.4559999999999995</v>
       </c>
       <c r="B34">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -4554,24 +4665,24 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>9.752000000000001</v>
+        <v>9.7569999999999997</v>
       </c>
       <c r="B35">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4580,24 +4691,24 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>10.054</v>
+        <v>10.06</v>
       </c>
       <c r="B36">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4606,24 +4717,24 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>10.356</v>
+        <v>10.362</v>
       </c>
       <c r="B37">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4632,24 +4743,24 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>10.66</v>
+        <v>10.666</v>
       </c>
       <c r="B38">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4658,24 +4769,24 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>10.961</v>
+        <v>10.968</v>
       </c>
       <c r="B39">
-        <v>253</v>
+        <v>120</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -4684,24 +4795,24 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>11.263</v>
+        <v>11.27</v>
       </c>
       <c r="B40">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4710,24 +4821,24 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>11.565</v>
+        <v>11.571999999999999</v>
       </c>
       <c r="B41">
-        <v>253</v>
+        <v>120</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -4736,24 +4847,24 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>11.867</v>
+        <v>11.874000000000001</v>
       </c>
       <c r="B42">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -4762,24 +4873,24 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>12.171</v>
+        <v>12.178000000000001</v>
       </c>
       <c r="B43">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -4788,24 +4899,24 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>12.472</v>
+        <v>12.48</v>
       </c>
       <c r="B44">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -4814,24 +4925,24 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>12.774</v>
+        <v>12.782</v>
       </c>
       <c r="B45">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -4840,24 +4951,24 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>13.076</v>
+        <v>13.084</v>
       </c>
       <c r="B46">
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -4866,24 +4977,24 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>13.379</v>
+        <v>13.387</v>
       </c>
       <c r="B47">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -4892,154 +5003,154 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>13.683</v>
+        <v>13.691000000000001</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="F48">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>13.985</v>
+        <v>13.993</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="F49">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>14.287</v>
+        <v>14.295</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>854</v>
       </c>
       <c r="F50">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>14.588</v>
+        <v>14.597</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="F51">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>14.89</v>
+        <v>14.898999999999999</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>854</v>
       </c>
       <c r="F52">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>15.194</v>
+        <v>15.202999999999999</v>
       </c>
       <c r="B53">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -5057,15 +5168,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>15.496</v>
+        <v>15.505000000000001</v>
       </c>
       <c r="B54">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -5083,15 +5194,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>15.798</v>
+        <v>15.805999999999999</v>
       </c>
       <c r="B55">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -5109,15 +5220,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>16.099</v>
+        <v>16.108000000000001</v>
       </c>
       <c r="B56">
-        <v>251</v>
+        <v>121</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -5135,15 +5246,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>16.401</v>
+        <v>16.41</v>
       </c>
       <c r="B57">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -5161,145 +5272,145 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>16.706</v>
+        <v>16.715</v>
       </c>
       <c r="B58">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D58">
-        <v>743</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="H58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>17.008</v>
+        <v>17.016999999999999</v>
       </c>
       <c r="B59">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C59">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D59">
-        <v>739</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>17.31</v>
+        <v>17.318999999999999</v>
       </c>
       <c r="B60">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C60">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D60">
-        <v>741</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>17.612</v>
+        <v>17.620999999999999</v>
       </c>
       <c r="B61">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C61">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D61">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>17.914</v>
+        <v>17.922999999999998</v>
       </c>
       <c r="B62">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D62">
-        <v>739</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>18.218</v>
+        <v>18.227</v>
       </c>
       <c r="B63">
-        <v>251</v>
+        <v>120</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -5317,15 +5428,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>18.519</v>
+        <v>18.529</v>
       </c>
       <c r="B64">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -5343,15 +5454,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>18.821</v>
+        <v>18.831</v>
       </c>
       <c r="B65">
-        <v>252</v>
+        <v>119</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -5369,15 +5480,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>19.123</v>
+        <v>19.132999999999999</v>
       </c>
       <c r="B66">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -5395,15 +5506,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>19.425</v>
+        <v>19.434999999999999</v>
       </c>
       <c r="B67">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="C67">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -5421,151 +5532,151 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>19.728</v>
+        <v>19.739000000000001</v>
       </c>
       <c r="B68">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="F68">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>20.03</v>
+        <v>20.042000000000002</v>
       </c>
       <c r="B69">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="F69">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>20.333</v>
+        <v>20.344000000000001</v>
       </c>
       <c r="B70">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="F70">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H70">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>20.635</v>
+        <v>20.646000000000001</v>
       </c>
       <c r="B71">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="F71">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>20.937</v>
+        <v>20.948</v>
       </c>
       <c r="B72">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="F72">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>21.241</v>
+        <v>21.251999999999999</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D73">
-        <v>994</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -5574,58 +5685,6 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74">
-        <v>21.543</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
-        <v>992</v>
-      </c>
-      <c r="E74">
-        <v>16</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75">
-        <v>21.844</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
-      </c>
-      <c r="D75">
-        <v>991</v>
-      </c>
-      <c r="E75">
-        <v>16</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="H75">
         <v>0</v>
       </c>
     </row>
